--- a/Status El Nino BB 6.xlsx
+++ b/Status El Nino BB 6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjrodrir\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62E2761-FF8A-41C4-B6F6-EAC951E99E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592550A4-07E5-49AE-A6E9-B95DC400E0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9919" uniqueCount="2036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10020" uniqueCount="2085">
   <si>
     <t>COD</t>
   </si>
@@ -6162,16 +6162,163 @@
     <t>Dentro de C.C.</t>
   </si>
   <si>
-    <t>Critico*</t>
-  </si>
-  <si>
-    <t>Lugar alta suceptibilidad a inundaciones, pero locales altos</t>
-  </si>
-  <si>
-    <t>Medio-alto</t>
-  </si>
-  <si>
-    <t>Lugar alta suceptibilidad a inundaciones</t>
+    <t>Historicamente se inundo</t>
+  </si>
+  <si>
+    <t>Se inunda la calle, pero local es un poco elevado</t>
+  </si>
+  <si>
+    <t>Ligera inundacion, local elevado</t>
+  </si>
+  <si>
+    <t>Se inunda la calle, pero local es elevado</t>
+  </si>
+  <si>
+    <t>Se inunda bien la calle</t>
+  </si>
+  <si>
+    <t>Registros de inundaciones a un par de cuadras pero el area es bastante grande y con bajadas</t>
+  </si>
+  <si>
+    <t>Se inundan los alrededores, es una pendiente bastante alta, puede ser seguro pero lleva corrientes</t>
+  </si>
+  <si>
+    <t>Todo cemento, alta posibilidad de tapar alcantarillas e inundacinoes, pero construcciones elevadas</t>
+  </si>
+  <si>
+    <t>Area de inundaciones, pero lugar amurallado y elevado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se inunda la calle y </t>
+  </si>
+  <si>
+    <t>Area propenso a inundaciones pero locales elevados</t>
+  </si>
+  <si>
+    <t>Bastante amurallado</t>
+  </si>
+  <si>
+    <t>Cercania a Rio Daule</t>
+  </si>
+  <si>
+    <t>Zona con cercanias a inundaciones, pero alto</t>
+  </si>
+  <si>
+    <t>Inundacion calles cercanas, edificaciones elevadas</t>
+  </si>
+  <si>
+    <t>Se inundan calles, edificio muy elevado</t>
+  </si>
+  <si>
+    <t>Revision fisica pendiente, maps desactualizado</t>
+  </si>
+  <si>
+    <t>Se inunda esa dseccion de la Juantancamarengo pero la primax es elevada</t>
+  </si>
+  <si>
+    <t>Se inunda calle, induauto es elevado</t>
+  </si>
+  <si>
+    <t>Alto riesgo en caso de inundarse la calle</t>
+  </si>
+  <si>
+    <t>Lugar elevado del punto BB</t>
+  </si>
+  <si>
+    <t>Hay un desague pluvial grande, de funcionar no hay problema</t>
+  </si>
+  <si>
+    <t>Algo elevado la ubicación, zona de calles inundadas</t>
+  </si>
+  <si>
+    <t>Es una zona baja a los alrededores</t>
+  </si>
+  <si>
+    <t>Zona de calles inundables, ubicación alta</t>
+  </si>
+  <si>
+    <t>Zona de calles inundables, dentro de comisariato de altura baja</t>
+  </si>
+  <si>
+    <t>Dentro de C.C. pero zona baja</t>
+  </si>
+  <si>
+    <t>Cernaia a calles inundables, local sin mucha altura</t>
+  </si>
+  <si>
+    <t>Punto dentro de Local con altura considerable</t>
+  </si>
+  <si>
+    <t>Se inundan calles, atm en exterior, sin mucha altura</t>
+  </si>
+  <si>
+    <t>Cllaes inundables, atm dentro de plaza con altura, exterior local, pero con mucha altura sobre pared ladrillada</t>
+  </si>
+  <si>
+    <t>Dentro de local Altoque, altura considerable</t>
+  </si>
+  <si>
+    <t>ChecameLuego Crack</t>
+  </si>
+  <si>
+    <t>Calles propension a inundacion, atm en local, con gran altura</t>
+  </si>
+  <si>
+    <t>Lugar propenso a inundaciones, pero altura del atm altp</t>
+  </si>
+  <si>
+    <t>Area muy inundable, alta suceptibilidad, varios historicos, cajero externo, puerta externa</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Inundaciones por la zona, atm se encuentra dentro de local altura baja</t>
+  </si>
+  <si>
+    <t>Cajero externo, altura vereda, puerta junto al atm</t>
+  </si>
+  <si>
+    <t>Zona propensa a inundaciones, altura gasolinera, atm dentro de Listo</t>
+  </si>
+  <si>
+    <t>Solo estaria en peligro si sube mucho el nivel del rio y tapa los desagues</t>
+  </si>
+  <si>
+    <t>Primax altura, dentro de local de Listo</t>
+  </si>
+  <si>
+    <t>ATM externo pero muy elevado en la zona cerca de 1.5m</t>
+  </si>
+  <si>
+    <t>Calle principal inundable a 2 locales del atm, externo no muy eleveado en fachada</t>
+  </si>
+  <si>
+    <t>Area media inundable, pero atm externo a hipermarket de bastante altura</t>
+  </si>
+  <si>
+    <t>ATM externo con cuarto, se ve construccion de un murito para lidiar con inundaciones, pero no presenta aun con eso gran altura, puede cerrarse</t>
+  </si>
+  <si>
+    <t>Area proximidad a inundacioens, pero atm interno a Listo y altura considerable</t>
+  </si>
+  <si>
+    <t>Altura considerable, 2 escalones de vereda, revisar dentro del lugar</t>
+  </si>
+  <si>
+    <t>Listo sin subida de altura</t>
+  </si>
+  <si>
+    <t>Media-Baja</t>
+  </si>
+  <si>
+    <t>Cajero externo, altura decente, 2 escalones de vereda, empotrado en pared</t>
+  </si>
+  <si>
+    <t>Dentro de hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atm externo empotrado pero sin mucha altura </t>
   </si>
 </sst>
 </file>
@@ -6179,7 +6326,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -6218,7 +6365,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
@@ -6228,8 +6375,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -6254,7 +6401,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cierre de saldos"/>
@@ -13543,12 +13689,15 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15"/>
-    <col min="2" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="11" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="11.42578125" customWidth="1"/>
     <col min="12" max="12" width="42.140625" customWidth="1"/>
-    <col min="13" max="14" width="15"/>
+    <col min="13" max="13" width="24.42578125" customWidth="1"/>
+    <col min="14" max="14" width="26.7109375" customWidth="1"/>
     <col min="16" max="17" width="15"/>
     <col min="18" max="18" width="11.42578125" customWidth="1"/>
     <col min="19" max="19" width="21.28515625" customWidth="1"/>
@@ -14249,6 +14398,12 @@
       <c r="B9" t="s">
         <v>196</v>
       </c>
+      <c r="C9" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2014</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>1998</v>
       </c>
@@ -14657,6 +14812,12 @@
       <c r="B14" t="s">
         <v>387</v>
       </c>
+      <c r="C14" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2003</v>
+      </c>
       <c r="E14" s="3" t="s">
         <v>1997</v>
       </c>
@@ -14741,6 +14902,12 @@
       <c r="B15" t="s">
         <v>538</v>
       </c>
+      <c r="C15" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2003</v>
+      </c>
       <c r="E15" s="3" t="s">
         <v>1998</v>
       </c>
@@ -15236,6 +15403,12 @@
       <c r="B21" t="s">
         <v>376</v>
       </c>
+      <c r="C21" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2014</v>
+      </c>
       <c r="E21" s="3" t="s">
         <v>2001</v>
       </c>
@@ -15482,6 +15655,12 @@
       <c r="B24" t="s">
         <v>973</v>
       </c>
+      <c r="C24" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2003</v>
+      </c>
       <c r="E24" s="3" t="s">
         <v>1997</v>
       </c>
@@ -15641,6 +15820,12 @@
       <c r="B26" t="s">
         <v>1046</v>
       </c>
+      <c r="C26" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1996</v>
+      </c>
       <c r="E26" s="3" t="s">
         <v>1997</v>
       </c>
@@ -15812,6 +15997,9 @@
       <c r="B28" t="s">
         <v>1041</v>
       </c>
+      <c r="D28" t="s">
+        <v>1990</v>
+      </c>
       <c r="E28" s="3" t="s">
         <v>1997</v>
       </c>
@@ -16232,9 +16420,6 @@
       <c r="B33" t="s">
         <v>933</v>
       </c>
-      <c r="D33" t="s">
-        <v>2032</v>
-      </c>
       <c r="G33" t="s">
         <v>98</v>
       </c>
@@ -16397,6 +16582,12 @@
       <c r="B35" t="s">
         <v>1072</v>
       </c>
+      <c r="C35" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2003</v>
+      </c>
       <c r="E35" s="3" t="s">
         <v>1997</v>
       </c>
@@ -17336,6 +17527,9 @@
       <c r="B46" t="s">
         <v>996</v>
       </c>
+      <c r="D46" t="s">
+        <v>1996</v>
+      </c>
       <c r="E46" s="3" t="s">
         <v>1997</v>
       </c>
@@ -18005,6 +18199,12 @@
       <c r="B54" t="s">
         <v>812</v>
       </c>
+      <c r="C54" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2003</v>
+      </c>
       <c r="E54" s="3" t="s">
         <v>1997</v>
       </c>
@@ -18332,6 +18532,9 @@
       <c r="B58" t="s">
         <v>402</v>
       </c>
+      <c r="D58" t="s">
+        <v>2003</v>
+      </c>
       <c r="E58" s="3" t="s">
         <v>2000</v>
       </c>
@@ -18590,6 +18793,12 @@
       <c r="B61" t="s">
         <v>599</v>
       </c>
+      <c r="C61" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2003</v>
+      </c>
       <c r="E61" s="3" t="s">
         <v>1997</v>
       </c>
@@ -18674,6 +18883,12 @@
       <c r="B62" t="s">
         <v>1107</v>
       </c>
+      <c r="C62" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2003</v>
+      </c>
       <c r="E62" s="3" t="s">
         <v>1997</v>
       </c>
@@ -18932,6 +19147,12 @@
       <c r="B65" t="s">
         <v>928</v>
       </c>
+      <c r="C65" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1994</v>
+      </c>
       <c r="E65" s="3" t="s">
         <v>1997</v>
       </c>
@@ -19340,6 +19561,12 @@
       <c r="B70" t="s">
         <v>1016</v>
       </c>
+      <c r="C70" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2003</v>
+      </c>
       <c r="E70" s="3" t="s">
         <v>1991</v>
       </c>
@@ -19511,6 +19738,12 @@
       <c r="B72" t="s">
         <v>209</v>
       </c>
+      <c r="C72" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2003</v>
+      </c>
       <c r="E72" s="3" t="s">
         <v>2006</v>
       </c>
@@ -19853,6 +20086,12 @@
       <c r="B76" t="s">
         <v>478</v>
       </c>
+      <c r="C76" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1996</v>
+      </c>
       <c r="E76" s="3" t="s">
         <v>1997</v>
       </c>
@@ -20114,6 +20353,12 @@
       <c r="B79" t="s">
         <v>872</v>
       </c>
+      <c r="C79" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2003</v>
+      </c>
       <c r="E79" s="3" t="s">
         <v>1997</v>
       </c>
@@ -20867,6 +21112,12 @@
       <c r="B88" t="s">
         <v>1011</v>
       </c>
+      <c r="C88" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2014</v>
+      </c>
       <c r="E88" t="s">
         <v>2001</v>
       </c>
@@ -21455,6 +21706,12 @@
       <c r="B95" t="s">
         <v>822</v>
       </c>
+      <c r="C95" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1996</v>
+      </c>
       <c r="E95" s="3" t="s">
         <v>2001</v>
       </c>
@@ -21626,6 +21883,12 @@
       <c r="B97" t="s">
         <v>1067</v>
       </c>
+      <c r="C97" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D97" t="s">
+        <v>2003</v>
+      </c>
       <c r="E97" s="3" t="s">
         <v>1997</v>
       </c>
@@ -22220,6 +22483,9 @@
       <c r="B104" t="s">
         <v>852</v>
       </c>
+      <c r="D104" t="s">
+        <v>1990</v>
+      </c>
       <c r="E104" s="3" t="s">
         <v>2000</v>
       </c>
@@ -22388,6 +22654,12 @@
       <c r="B106" t="s">
         <v>719</v>
       </c>
+      <c r="C106" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2014</v>
+      </c>
       <c r="E106" s="3" t="s">
         <v>2009</v>
       </c>
@@ -22721,6 +22993,12 @@
       <c r="B110" t="s">
         <v>1001</v>
       </c>
+      <c r="C110" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1996</v>
+      </c>
       <c r="E110" s="3" t="s">
         <v>1997</v>
       </c>
@@ -22892,6 +23170,12 @@
       <c r="B112" t="s">
         <v>371</v>
       </c>
+      <c r="C112" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D112" t="s">
+        <v>2003</v>
+      </c>
       <c r="E112" s="3" t="s">
         <v>1997</v>
       </c>
@@ -23225,6 +23509,9 @@
       <c r="B116" t="s">
         <v>731</v>
       </c>
+      <c r="D116" t="s">
+        <v>1995</v>
+      </c>
       <c r="E116" s="3" t="s">
         <v>1998</v>
       </c>
@@ -23309,6 +23596,12 @@
       <c r="B117" t="s">
         <v>968</v>
       </c>
+      <c r="C117" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2014</v>
+      </c>
       <c r="E117" s="3" t="s">
         <v>1997</v>
       </c>
@@ -23393,6 +23686,12 @@
       <c r="B118" t="s">
         <v>498</v>
       </c>
+      <c r="C118" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1996</v>
+      </c>
       <c r="E118" s="3" t="s">
         <v>1997</v>
       </c>
@@ -23810,6 +24109,12 @@
       <c r="B123" t="s">
         <v>444</v>
       </c>
+      <c r="C123" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1995</v>
+      </c>
       <c r="E123" s="3" t="s">
         <v>1997</v>
       </c>
@@ -23975,6 +24280,9 @@
       <c r="B125" t="s">
         <v>473</v>
       </c>
+      <c r="D125" t="s">
+        <v>1990</v>
+      </c>
       <c r="E125" s="3" t="s">
         <v>1998</v>
       </c>
@@ -24389,6 +24697,12 @@
       <c r="B130" t="s">
         <v>459</v>
       </c>
+      <c r="C130" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D130" t="s">
+        <v>2003</v>
+      </c>
       <c r="E130" s="3" t="s">
         <v>1998</v>
       </c>
@@ -24473,6 +24787,12 @@
       <c r="B131" t="s">
         <v>659</v>
       </c>
+      <c r="C131" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1996</v>
+      </c>
       <c r="E131" s="3" t="s">
         <v>1998</v>
       </c>
@@ -24728,6 +25048,12 @@
       <c r="B134" t="s">
         <v>908</v>
       </c>
+      <c r="C134" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1996</v>
+      </c>
       <c r="E134" s="3" t="s">
         <v>1997</v>
       </c>
@@ -24812,6 +25138,12 @@
       <c r="B135" t="s">
         <v>503</v>
       </c>
+      <c r="C135" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1996</v>
+      </c>
       <c r="E135" s="3" t="s">
         <v>1997</v>
       </c>
@@ -25133,9 +25465,6 @@
       <c r="B139" t="s">
         <v>736</v>
       </c>
-      <c r="D139" t="s">
-        <v>2003</v>
-      </c>
       <c r="E139" s="3" t="s">
         <v>1997</v>
       </c>
@@ -25880,6 +26209,9 @@
       <c r="B148" t="s">
         <v>664</v>
       </c>
+      <c r="C148" t="s">
+        <v>2032</v>
+      </c>
       <c r="D148" t="s">
         <v>1994</v>
       </c>
@@ -26054,6 +26386,9 @@
       <c r="B150" t="s">
         <v>407</v>
       </c>
+      <c r="D150" t="s">
+        <v>2003</v>
+      </c>
       <c r="E150" s="3" t="s">
         <v>2000</v>
       </c>
@@ -26138,6 +26473,12 @@
       <c r="B151" t="s">
         <v>190</v>
       </c>
+      <c r="C151" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1996</v>
+      </c>
       <c r="E151" s="3" t="s">
         <v>1998</v>
       </c>
@@ -26384,6 +26725,12 @@
       <c r="B154" t="s">
         <v>172</v>
       </c>
+      <c r="C154" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D154" t="s">
+        <v>2014</v>
+      </c>
       <c r="E154" s="3" t="s">
         <v>1998</v>
       </c>
@@ -26549,6 +26896,9 @@
       <c r="B156" t="s">
         <v>65</v>
       </c>
+      <c r="D156" t="s">
+        <v>2064</v>
+      </c>
       <c r="E156" s="3" t="s">
         <v>1997</v>
       </c>
@@ -26891,6 +27241,12 @@
       <c r="B160" t="s">
         <v>792</v>
       </c>
+      <c r="C160" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1996</v>
+      </c>
       <c r="E160" s="3" t="s">
         <v>1997</v>
       </c>
@@ -27137,6 +27493,12 @@
       <c r="B163" t="s">
         <v>553</v>
       </c>
+      <c r="C163" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1996</v>
+      </c>
       <c r="E163" s="3" t="s">
         <v>2000</v>
       </c>
@@ -27308,6 +27670,12 @@
       <c r="B165" t="s">
         <v>639</v>
       </c>
+      <c r="C165" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1996</v>
+      </c>
       <c r="E165" s="3" t="s">
         <v>1997</v>
       </c>
@@ -28079,6 +28447,12 @@
       <c r="B174" t="s">
         <v>767</v>
       </c>
+      <c r="C174" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D174" t="s">
+        <v>2081</v>
+      </c>
       <c r="E174" s="3" t="s">
         <v>2006</v>
       </c>
@@ -29495,6 +29869,12 @@
       <c r="B191" t="s">
         <v>345</v>
       </c>
+      <c r="C191" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1996</v>
+      </c>
       <c r="E191" s="3" t="s">
         <v>2009</v>
       </c>
@@ -29834,6 +30214,12 @@
       <c r="B195" t="s">
         <v>320</v>
       </c>
+      <c r="C195" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D195" t="s">
+        <v>2014</v>
+      </c>
       <c r="E195" s="3" t="s">
         <v>2001</v>
       </c>
@@ -30092,6 +30478,12 @@
       <c r="B198" t="s">
         <v>685</v>
       </c>
+      <c r="C198" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1996</v>
+      </c>
       <c r="E198" s="3" t="s">
         <v>1998</v>
       </c>
@@ -30257,6 +30649,12 @@
       <c r="B200" t="s">
         <v>272</v>
       </c>
+      <c r="C200" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D200" t="s">
+        <v>2014</v>
+      </c>
       <c r="E200" s="3" t="s">
         <v>1997</v>
       </c>
@@ -30341,9 +30739,6 @@
       <c r="B201" t="s">
         <v>488</v>
       </c>
-      <c r="D201" t="s">
-        <v>1990</v>
-      </c>
       <c r="E201" t="s">
         <v>2005</v>
       </c>
@@ -30428,6 +30823,9 @@
       <c r="B202" t="s">
         <v>464</v>
       </c>
+      <c r="D202" t="s">
+        <v>1996</v>
+      </c>
       <c r="E202" s="3" t="s">
         <v>1997</v>
       </c>
@@ -31517,6 +31915,12 @@
       <c r="B215" t="s">
         <v>614</v>
       </c>
+      <c r="C215" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1996</v>
+      </c>
       <c r="E215" s="3" t="s">
         <v>1998</v>
       </c>
@@ -32200,18 +32604,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>391</v>
       </c>
       <c r="B223" t="s">
         <v>335</v>
-      </c>
-      <c r="C223" t="s">
-        <v>2035</v>
-      </c>
-      <c r="D223" t="s">
-        <v>2034</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>1998</v>
@@ -32297,6 +32695,12 @@
       <c r="B224" t="s">
         <v>229</v>
       </c>
+      <c r="C224" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1996</v>
+      </c>
       <c r="E224" s="3" t="s">
         <v>2006</v>
       </c>
@@ -32630,6 +33034,9 @@
       <c r="B228" t="s">
         <v>943</v>
       </c>
+      <c r="D228" t="s">
+        <v>1990</v>
+      </c>
       <c r="E228" s="3" t="s">
         <v>1998</v>
       </c>
@@ -32801,6 +33208,9 @@
       <c r="B230" t="s">
         <v>355</v>
       </c>
+      <c r="D230" t="s">
+        <v>1996</v>
+      </c>
       <c r="E230" s="3" t="s">
         <v>2006</v>
       </c>
@@ -32972,6 +33382,12 @@
       <c r="B232" t="s">
         <v>634</v>
       </c>
+      <c r="C232" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1996</v>
+      </c>
       <c r="E232" s="3" t="s">
         <v>2006</v>
       </c>
@@ -33386,6 +33802,12 @@
       <c r="B237" t="s">
         <v>695</v>
       </c>
+      <c r="C237" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D237" t="s">
+        <v>2002</v>
+      </c>
       <c r="E237" s="3" t="s">
         <v>2001</v>
       </c>
@@ -33800,12 +34222,6 @@
       <c r="B242" t="s">
         <v>365</v>
       </c>
-      <c r="C242" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D242" t="s">
-        <v>2003</v>
-      </c>
       <c r="E242" s="3" t="s">
         <v>2006</v>
       </c>
@@ -34145,6 +34561,12 @@
       <c r="B246" t="s">
         <v>938</v>
       </c>
+      <c r="C246" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D246" t="s">
+        <v>2003</v>
+      </c>
       <c r="E246" s="3" t="s">
         <v>1997</v>
       </c>
@@ -34229,6 +34651,12 @@
       <c r="B247" t="s">
         <v>923</v>
       </c>
+      <c r="C247" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D247" t="s">
+        <v>2003</v>
+      </c>
       <c r="E247" s="3" t="s">
         <v>1997</v>
       </c>
@@ -34313,12 +34741,6 @@
       <c r="B248" t="s">
         <v>700</v>
       </c>
-      <c r="C248" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D248" t="s">
-        <v>2003</v>
-      </c>
       <c r="E248" s="3" t="s">
         <v>2006</v>
       </c>
@@ -35231,9 +35653,6 @@
       <c r="B259" t="s">
         <v>842</v>
       </c>
-      <c r="D259" t="s">
-        <v>1990</v>
-      </c>
       <c r="E259" s="3" t="s">
         <v>1997</v>
       </c>
@@ -35318,6 +35737,12 @@
       <c r="B260" t="s">
         <v>963</v>
       </c>
+      <c r="C260" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D260" t="s">
+        <v>2014</v>
+      </c>
       <c r="E260" s="3" t="s">
         <v>1997</v>
       </c>
@@ -35900,12 +36325,6 @@
       <c r="B267" t="s">
         <v>619</v>
       </c>
-      <c r="C267" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D267" t="s">
-        <v>1996</v>
-      </c>
       <c r="E267" s="3" t="s">
         <v>2006</v>
       </c>
@@ -36251,9 +36670,6 @@
       <c r="B271" t="s">
         <v>1056</v>
       </c>
-      <c r="D271" t="s">
-        <v>1996</v>
-      </c>
       <c r="E271" t="s">
         <v>2008</v>
       </c>
@@ -36338,6 +36754,12 @@
       <c r="B272" t="s">
         <v>1128</v>
       </c>
+      <c r="C272" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D272" t="s">
+        <v>2003</v>
+      </c>
       <c r="E272" s="3" t="s">
         <v>1997</v>
       </c>
@@ -36422,6 +36844,9 @@
       <c r="B273" t="s">
         <v>958</v>
       </c>
+      <c r="D273" t="s">
+        <v>1990</v>
+      </c>
       <c r="E273" s="3" t="s">
         <v>2009</v>
       </c>
@@ -36590,6 +37015,12 @@
       <c r="B275" t="s">
         <v>360</v>
       </c>
+      <c r="C275" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D275" t="s">
+        <v>2003</v>
+      </c>
       <c r="E275" s="3" t="s">
         <v>2006</v>
       </c>
@@ -36680,9 +37111,6 @@
       <c r="B276" t="s">
         <v>714</v>
       </c>
-      <c r="D276" t="s">
-        <v>2014</v>
-      </c>
       <c r="E276" t="s">
         <v>1998</v>
       </c>
@@ -36767,12 +37195,6 @@
       <c r="B277" t="s">
         <v>154</v>
       </c>
-      <c r="C277" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D277" t="s">
-        <v>2003</v>
-      </c>
       <c r="E277" s="3" t="s">
         <v>2006</v>
       </c>
@@ -36857,6 +37279,9 @@
       <c r="B278" t="s">
         <v>690</v>
       </c>
+      <c r="D278" t="s">
+        <v>2014</v>
+      </c>
       <c r="E278" s="3" t="s">
         <v>1991</v>
       </c>
@@ -37329,9 +37754,6 @@
       <c r="B284" t="s">
         <v>1976</v>
       </c>
-      <c r="D284" t="s">
-        <v>2003</v>
-      </c>
       <c r="E284" t="s">
         <v>2017</v>
       </c>
@@ -38692,6 +39114,12 @@
       <c r="B301" t="s">
         <v>219</v>
       </c>
+      <c r="C301" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D301" t="s">
+        <v>2003</v>
+      </c>
       <c r="E301" s="3" t="s">
         <v>1998</v>
       </c>
@@ -38851,6 +39279,12 @@
       <c r="B303" t="s">
         <v>827</v>
       </c>
+      <c r="C303" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D303" t="s">
+        <v>2068</v>
+      </c>
       <c r="E303" s="3" t="s">
         <v>1997</v>
       </c>
@@ -38935,6 +39369,12 @@
       <c r="B304" t="s">
         <v>772</v>
       </c>
+      <c r="C304" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1996</v>
+      </c>
       <c r="E304" s="3" t="s">
         <v>1997</v>
       </c>
@@ -39106,6 +39546,12 @@
       <c r="B306" t="s">
         <v>724</v>
       </c>
+      <c r="C306" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1996</v>
+      </c>
       <c r="E306" s="3" t="s">
         <v>1997</v>
       </c>
@@ -39358,6 +39804,12 @@
       <c r="B309" t="s">
         <v>893</v>
       </c>
+      <c r="C309" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D309" t="s">
+        <v>2003</v>
+      </c>
       <c r="E309" s="3" t="s">
         <v>1997</v>
       </c>
@@ -40686,7 +41138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>1501</v>
       </c>
@@ -40866,7 +41318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>1532</v>
       </c>
@@ -42507,7 +42959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>1837</v>
       </c>
@@ -43020,7 +43472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>193</v>
       </c>
@@ -45561,7 +46013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>1743</v>
       </c>
@@ -45717,7 +46169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>1233</v>
       </c>
@@ -45804,7 +46256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>1749</v>
       </c>
@@ -45879,7 +46331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>1381</v>
       </c>
@@ -45966,7 +46418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>1359</v>
       </c>
@@ -46047,7 +46499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>1553</v>
       </c>
@@ -46134,7 +46586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>1755</v>
       </c>
@@ -46215,7 +46667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>1737</v>
       </c>
@@ -46290,7 +46742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>38</v>
       </c>
@@ -46371,7 +46823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>1713</v>
       </c>
@@ -46446,7 +46898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>1776</v>
       </c>
@@ -46521,7 +46973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
         <v>1782</v>
       </c>
@@ -46602,7 +47054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>1761</v>
       </c>
@@ -46677,7 +47129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>1276</v>
       </c>
@@ -46758,7 +47210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>1369</v>
       </c>
@@ -46845,7 +47297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>1770</v>
       </c>
@@ -46926,7 +47378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>158</v>
       </c>
@@ -47007,7 +47459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>141</v>
       </c>
@@ -47088,7 +47540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="400" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>135</v>
       </c>
@@ -47175,7 +47627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>1385</v>
       </c>
@@ -47256,7 +47708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>1702</v>
       </c>
@@ -47412,7 +47864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>151</v>
       </c>
@@ -47742,7 +48194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
         <v>1865</v>
       </c>
@@ -47817,7 +48269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1983</v>
       </c>
@@ -47906,22 +48358,59 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AE409" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ATM - DEL PORTAL LA JOYA"/>
+        <filter val="A0010"/>
+        <filter val="A0012"/>
+        <filter val="A0032"/>
+        <filter val="A0039"/>
+        <filter val="A0073"/>
+        <filter val="A0075"/>
+        <filter val="A0076"/>
+        <filter val="A0077"/>
+        <filter val="A0078"/>
+        <filter val="A0079"/>
+        <filter val="A0080"/>
+        <filter val="A0081"/>
+        <filter val="A0082"/>
+        <filter val="A0083"/>
+        <filter val="A0084"/>
+        <filter val="A0085"/>
+        <filter val="A0086"/>
+        <filter val="A0087"/>
+        <filter val="A0088"/>
+        <filter val="A0089"/>
+        <filter val="A0090"/>
+        <filter val="A0091"/>
+        <filter val="A0092"/>
+        <filter val="A0097"/>
+        <filter val="A0098"/>
+        <filter val="A0100"/>
+        <filter val="A0106"/>
+        <filter val="A0107"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
       <filters blank="1"/>
     </filterColumn>
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Bajo / Seguro"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="14">
       <filters>
-        <filter val="Esmeraldas"/>
-        <filter val="Galápagos"/>
-        <filter val="Guayas"/>
-        <filter val="Los Ríos"/>
-        <filter val="Manabí"/>
-        <filter val="Santa Elena"/>
+        <filter val="Azuay"/>
+        <filter val="Cañar"/>
+        <filter val="Cotopaxi"/>
+        <filter val="Imbabura"/>
+        <filter val="Loja"/>
+        <filter val="Pichincha"/>
+        <filter val="Santo Domingo de los Tsáchilas"/>
+        <filter val="Tungurahua"/>
       </filters>
     </filterColumn>
   </autoFilter>
